--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_28.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_28.xlsx
@@ -471,16 +471,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71469</v>
+        <v>17254</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Esther Campos</t>
+          <t>Ana Lívia Nunes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,56 +489,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45078</v>
+        <v>45102</v>
       </c>
       <c r="G2" t="n">
-        <v>7010.87</v>
+        <v>9850.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24482</v>
+        <v>98225</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ana Julia Barbosa</t>
+          <t>Alexandre das Neves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45104</v>
+        <v>45100</v>
       </c>
       <c r="G3" t="n">
-        <v>2667.38</v>
+        <v>8864.120000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53091</v>
+        <v>1967</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luiz Otávio da Cruz</t>
+          <t>Isis Nascimento</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,27 +547,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45080</v>
+        <v>45089</v>
       </c>
       <c r="G4" t="n">
-        <v>11852.88</v>
+        <v>7581.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84539</v>
+        <v>20129</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maria Clara da Paz</t>
+          <t>Giovanna Aragão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,114 +576,114 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45088</v>
+        <v>45082</v>
       </c>
       <c r="G5" t="n">
-        <v>6741.15</v>
+        <v>7512.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>78128</v>
+        <v>68400</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luiz Otávio Viana</t>
+          <t>Calebe Lima</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45097</v>
+        <v>45100</v>
       </c>
       <c r="G6" t="n">
-        <v>6918.88</v>
+        <v>11292.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74558</v>
+        <v>37423</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sr. Paulo Sales</t>
+          <t>Rafaela Rocha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45102</v>
+        <v>45083</v>
       </c>
       <c r="G7" t="n">
-        <v>3804.86</v>
+        <v>3849.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6190</v>
+        <v>59699</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Barros</t>
+          <t>Júlia da Luz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45081</v>
+        <v>45103</v>
       </c>
       <c r="G8" t="n">
-        <v>3098.5</v>
+        <v>5239.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99152</v>
+        <v>9751</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maria Cecília Jesus</t>
+          <t>Maria Luiza Almeida</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -692,27 +692,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45079</v>
+        <v>45094</v>
       </c>
       <c r="G9" t="n">
-        <v>10631.7</v>
+        <v>12002.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20227</v>
+        <v>85212</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samuel Fogaça</t>
+          <t>Yuri Vieira</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,27 +721,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>45097</v>
       </c>
       <c r="G10" t="n">
-        <v>12171.26</v>
+        <v>7709.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17340</v>
+        <v>85393</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Natália Nogueira</t>
+          <t>Enzo Gabriel Barros</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45100</v>
+        <v>45106</v>
       </c>
       <c r="G11" t="n">
-        <v>4603.06</v>
+        <v>11822.91</v>
       </c>
     </row>
   </sheetData>
